--- a/outputs/tables/tab3_model.xlsx
+++ b/outputs/tables/tab3_model.xlsx
@@ -54,55 +54,55 @@
     <t xml:space="preserve">Post2022 × Net exporter</t>
   </si>
   <si>
-    <t xml:space="preserve">1.800†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.790†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">−0.323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.911)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.920)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.497)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.150)</t>
+    <t xml:space="preserve">1.331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">−0.091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.035)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.412)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.982)</t>
   </si>
   <si>
     <t xml:space="preserve">Post2022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.451*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.210)</t>
+    <t xml:space="preserve">0.624*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.260)</t>
   </si>
   <si>
     <t xml:space="preserve">Net exporter</t>
   </si>
   <si>
-    <t xml:space="preserve">2.873†</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1.444)</t>
+    <t xml:space="preserve">3.188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1.994)</t>
   </si>
   <si>
     <t xml:space="preserve">Constant</t>
   </si>
   <si>
-    <t xml:space="preserve">0.428**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(0.134)</t>
+    <t xml:space="preserve">0.553***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(0.147)</t>
   </si>
   <si>
     <t xml:space="preserve">Country FE</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">228</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes. β₃ (Post2022 × Net exporter) is the change in the subsidy of net oil exporters between the 2015–2021 average and 2022 in excess of the corresponding change among net oil importers (the comparison group). Dependent variable (% of GDP): explicit subsidy in columns (1)–(2), implicit in (3), and total in (4). Columns (2)–(4) include country and year fixed effects. For the implicit component, the effect is small and statistically insignificant. Standard errors are clustered by country in parentheses. † p &lt; 0.10, * p &lt; 0.05, ** p &lt; 0.01, *** p &lt; 0.001. Sample: 2015–2022 (34 countries; 30 in columns (3)–(4)). 2023, a reversal year (Brent fell from USD 100.9 to USD 82.5 per barrel), is excluded. Source: IMF Fossil Fuel Subsidies Database; U.S. Energy Information Administration (EIA).</t>
+    <t xml:space="preserve">Notes. β₃ (Post2022 × Net exporter) is the change in the subsidy of net oil exporters between the 2015–2021 average and 2022 in excess of the corresponding change among net oil importers (the comparison group). Dependent variable (% of GDP): explicit subsidy in columns (1)–(2), implicit in (3), and total in (4). Columns (2)–(4) include country and year fixed effects. For the implicit component, the effect is −0.09 pp of GDP and not statistically significant. Standard errors are clustered by country in parentheses. † p &lt; 0.10, * p &lt; 0.05, ** p &lt; 0.01, *** p &lt; 0.001. Sample: 2015–2022 (34 countries; 30 in columns (3)–(4)). 2023, a reversal year (Brent fell from USD 100.9 to USD 82.5 per barrel), is excluded. Source: IMF Fossil Fuel Subsidies Database; U.S. Energy Information Administration (EIA).</t>
   </si>
 </sst>
 </file>
@@ -759,7 +759,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="15" ht="75" customHeight="1">
+    <row r="15" ht="87.5" customHeight="1">
       <c r="B15" s="8" t="s">
         <v>36</v>
       </c>
